--- a/output/Template_Feb26.xlsx
+++ b/output/Template_Feb26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://telekom-my.sharepoint.de/personal/julian_buettner_t-systems_com/Documents/Desktop/Certificates/Python_Projects/-01-Projekt/Report_Automation_Public/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_CE6562AA0C012E47858B43047D6EFC0B91532D0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29C56553-41A8-4227-9366-7A300998712E}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_CE6562AA0C012E47858B43047D6EFC0B91532D0F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{523276C1-6351-4D3A-B804-CC70B0044EF7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="23976" yWindow="936" windowWidth="17280" windowHeight="8928" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -479,16 +479,20 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -501,10 +505,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -802,10 +802,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="37"/>
+      <c r="B4" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="27"/>
       <c r="G4" t="s">
         <v>1</v>
       </c>
@@ -832,7 +832,7 @@
     </row>
     <row r="9" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="28" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="29"/>
@@ -852,7 +852,7 @@
       <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="34">
         <v>2025</v>
       </c>
       <c r="D11" s="29"/>
@@ -864,10 +864,10 @@
       <c r="J11" s="29"/>
       <c r="K11" s="29"/>
       <c r="L11" s="30"/>
-      <c r="M11" s="26">
+      <c r="M11" s="31">
         <v>2026</v>
       </c>
-      <c r="N11" s="27"/>
+      <c r="N11" s="32"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
@@ -1070,24 +1070,24 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="37"/>
+      <c r="N16" s="37"/>
     </row>
     <row r="17" spans="2:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="28" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="29"/>
@@ -1107,7 +1107,7 @@
       <c r="B18" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="33">
         <v>2025</v>
       </c>
       <c r="D18" s="29"/>
@@ -1119,10 +1119,10 @@
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
       <c r="L18" s="30"/>
-      <c r="M18" s="33">
+      <c r="M18" s="35">
         <v>2026</v>
       </c>
-      <c r="N18" s="27"/>
+      <c r="N18" s="32"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
